--- a/data/trans_camb/P44-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P44-Provincia-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,74; 26,26</t>
+          <t>4,93; 24,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37,87; 57,83</t>
+          <t>37,8; 57,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 14,55</t>
+          <t>-4,97; 14,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,94; 24,24</t>
+          <t>8,28; 24,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 16,53</t>
+          <t>2,41; 16,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,11; 38,65</t>
+          <t>25,74; 38,36</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,42; 659,17</t>
+          <t>33,82; 642,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>249,7; 1535,47</t>
+          <t>255,79; 1600,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,3; 225,52</t>
+          <t>-33,93; 229,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42,05; 400,87</t>
+          <t>46,3; 436,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,53; 258,15</t>
+          <t>17,53; 259,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>174,2; 646,33</t>
+          <t>174,68; 590,37</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,61; -2,18</t>
+          <t>-17,07; -2,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,96; 27,42</t>
+          <t>8,42; 27,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,9; -2,54</t>
+          <t>-11,48; -2,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 12,58</t>
+          <t>1,89; 12,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,62; -3,11</t>
+          <t>-12,42; -3,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,53; 17,63</t>
+          <t>7,16; 17,31</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-82,38; -17,17</t>
+          <t>-83,15; -21,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47,44; 282,53</t>
+          <t>35,93; 265,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-89,9; -27,46</t>
+          <t>-90,34; -27,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,51; 187,93</t>
+          <t>13,9; 201,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-80,13; -31,3</t>
+          <t>-81,79; -42,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,33; 194,09</t>
+          <t>46,31; 193,96</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 15,32</t>
+          <t>-1,34; 14,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,07; 35,92</t>
+          <t>17,99; 35,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 10,98</t>
+          <t>-3,53; 12,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,53; 31,81</t>
+          <t>16,94; 31,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 11,06</t>
+          <t>-0,95; 10,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,91; 31,85</t>
+          <t>20,23; 31,83</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 388,94</t>
+          <t>-19,61; 360,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>124,47; 933,22</t>
+          <t>104,3; 737,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,92; 213,6</t>
+          <t>-35,04; 209,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>110,18; 608,95</t>
+          <t>113,7; 606,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 170,67</t>
+          <t>-8,72; 175,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>163,79; 563,3</t>
+          <t>159,73; 551,4</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 16,92</t>
+          <t>1,21; 16,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,32; 31,47</t>
+          <t>13,57; 31,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 8,36</t>
+          <t>-5,36; 8,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,31; 28,21</t>
+          <t>15,1; 28,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 9,82</t>
+          <t>-0,41; 9,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,29; 27,47</t>
+          <t>17,1; 27,46</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,38; 436,71</t>
+          <t>-1,92; 343,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>105,6; 712,84</t>
+          <t>87,96; 650,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-46,42; 135,01</t>
+          <t>-43,46; 146,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>106,42; 528,49</t>
+          <t>99,88; 491,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 163,01</t>
+          <t>-5,31; 162,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>145,1; 473,34</t>
+          <t>142,97; 472,72</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 2,3</t>
+          <t>-12,92; 2,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 16,98</t>
+          <t>-1,99; 16,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 2,6</t>
+          <t>-11,01; 2,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 12,19</t>
+          <t>-2,23; 12,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 0,65</t>
+          <t>-9,31; 0,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,47; 12,34</t>
+          <t>1,61; 12,31</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 143,33</t>
+          <t>-92,54; 206,85</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 453,6</t>
+          <t>-21,83; 429,3</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-90,05; 99,73</t>
+          <t>-90,97; 119,06</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,42; 405,94</t>
+          <t>-24,13; 357,52</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-84,2; 27,75</t>
+          <t>-83,56; 19,57</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,59; 275,95</t>
+          <t>13,12; 284,5</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 7,84</t>
+          <t>-8,33; 7,08</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>11,54; 27,41</t>
+          <t>10,87; 28,63</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 7,14</t>
+          <t>-4,12; 7,17</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12,43; 24,84</t>
+          <t>12,42; 24,78</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 5,42</t>
+          <t>-4,41; 5,05</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,32; 24,81</t>
+          <t>13,92; 24,67</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-63,11; 136,74</t>
+          <t>-62,92; 140,02</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>68,6; 507,38</t>
+          <t>58,13; 555,51</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-67,03; 281,21</t>
+          <t>-63,38; 305,18</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>129,38; 1308,52</t>
+          <t>134,34; 1004,19</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-45,11; 126,04</t>
+          <t>-49,22; 107,69</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>138,2; 544,15</t>
+          <t>129,96; 530,92</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,21; 14,0</t>
+          <t>1,94; 14,33</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>22,67; 36,28</t>
+          <t>22,36; 36,06</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 7,43</t>
+          <t>-2,32; 7,74</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 32,97</t>
+          <t>-3,2; 31,79</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,33; 9,48</t>
+          <t>1,12; 8,96</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,01; 31,24</t>
+          <t>4,61; 31,52</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>18,14; 290,27</t>
+          <t>14,0; 311,62</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>196,98; 794,33</t>
+          <t>198,86; 802,32</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-21,74; 143,87</t>
+          <t>-27,44; 141,88</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-25,77; 501,03</t>
+          <t>-27,04; 461,47</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>13,34; 163,53</t>
+          <t>8,29; 150,14</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>34,72; 470,83</t>
+          <t>59,79; 462,52</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 2,98</t>
+          <t>-7,42; 2,83</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>29,51; 79,77</t>
+          <t>29,24; 82,19</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 2,07</t>
+          <t>-4,4; 1,81</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>27,77; 36,97</t>
+          <t>27,54; 36,86</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 1,36</t>
+          <t>-4,53; 1,58</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>30,9; 71,97</t>
+          <t>30,36; 69,68</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-54,97; 39,14</t>
+          <t>-54,22; 38,62</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>250,89; 1183,5</t>
+          <t>249,98; 1647,92</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-62,66; 79,1</t>
+          <t>-66,38; 62,99</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>392,32; 1332,61</t>
+          <t>391,52; 1384,25</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-50,7; 25,46</t>
+          <t>-51,45; 29,57</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>386,91; 1445,5</t>
+          <t>369,59; 1251,06</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 4,69</t>
+          <t>-0,21; 4,71</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>26,39; 56,99</t>
+          <t>25,9; 55,91</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 1,8</t>
+          <t>-1,97; 1,96</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>10,15; 23,23</t>
+          <t>9,33; 22,98</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 2,54</t>
+          <t>-0,6; 2,69</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>21,08; 40,55</t>
+          <t>20,61; 40,95</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 57,89</t>
+          <t>-2,49; 56,63</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>260,36; 647,21</t>
+          <t>252,2; 661,52</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-22,95; 27,72</t>
+          <t>-23,62; 29,74</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>137,19; 336,2</t>
+          <t>140,99; 342,01</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 34,17</t>
+          <t>-5,74; 36,06</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>234,27; 487,57</t>
+          <t>233,98; 505,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P44-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P44-Provincia-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>48,49</t>
+          <t>44,98</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,74</t>
+          <t>16,51</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,47</t>
+          <t>30,8</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,93; 24,17</t>
+          <t>4,52; 26,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37,8; 57,44</t>
+          <t>34,48; 54,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 14,83</t>
+          <t>-5,4; 13,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,28; 24,38</t>
+          <t>7,18; 24,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,41; 16,65</t>
+          <t>1,85; 16,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,74; 38,36</t>
+          <t>24,71; 37,17</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>596,11%</t>
+          <t>552,93%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>156,13%</t>
+          <t>154,02%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>340,05%</t>
+          <t>322,58%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,82; 642,63</t>
+          <t>30,56; 656,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>255,79; 1600,22</t>
+          <t>221,97; 1427,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-33,93; 229,59</t>
+          <t>-36,87; 223,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46,3; 436,89</t>
+          <t>40,0; 405,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,53; 259,73</t>
+          <t>9,51; 247,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>174,68; 590,37</t>
+          <t>173,68; 594,11</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>18,14</t>
+          <t>17,69</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,29</t>
+          <t>7,48</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,3</t>
+          <t>12,2</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,07; -2,48</t>
+          <t>-16,26; -2,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,42; 27,4</t>
+          <t>8,98; 26,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,48; -2,43</t>
+          <t>-11,88; -2,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 12,9</t>
+          <t>2,16; 12,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,42; -3,94</t>
+          <t>-12,1; -3,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,16; 17,31</t>
+          <t>7,14; 17,14</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>130,17%</t>
+          <t>126,93%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>106,81%</t>
+          <t>105,88%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-83,15; -21,43</t>
+          <t>-83,72; -16,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,93; 265,8</t>
+          <t>45,07; 285,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-90,34; -27,72</t>
+          <t>-91,28; -34,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,9; 201,82</t>
+          <t>15,6; 199,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-81,79; -42,53</t>
+          <t>-81,75; -38,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,31; 193,96</t>
+          <t>46,14; 189,23</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27,86</t>
+          <t>27,76</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24,75</t>
+          <t>25,37</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,22</t>
+          <t>26,48</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 14,92</t>
+          <t>-1,43; 15,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,99; 35,31</t>
+          <t>19,89; 35,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 12,05</t>
+          <t>-3,39; 12,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,94; 31,6</t>
+          <t>17,68; 32,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 10,3</t>
+          <t>-0,7; 10,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,23; 31,83</t>
+          <t>20,98; 31,58</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>340,81%</t>
+          <t>339,7%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>277,0%</t>
+          <t>283,87%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>304,66%</t>
+          <t>307,67%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,61; 360,62</t>
+          <t>-17,14; 358,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>104,3; 737,43</t>
+          <t>141,44; 926,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,04; 209,24</t>
+          <t>-33,91; 215,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>113,7; 606,09</t>
+          <t>122,05; 552,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 175,97</t>
+          <t>-7,6; 187,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>159,73; 551,4</t>
+          <t>162,01; 548,76</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>23,38</t>
+          <t>23,36</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21,73</t>
+          <t>21,7</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,5</t>
+          <t>22,47</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 16,16</t>
+          <t>0,85; 16,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,57; 31,05</t>
+          <t>15,02; 31,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 8,66</t>
+          <t>-5,22; 8,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,1; 28,1</t>
+          <t>14,73; 28,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 9,93</t>
+          <t>0,29; 10,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,1; 27,46</t>
+          <t>17,41; 27,63</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>296,44%</t>
+          <t>296,19%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>235,81%</t>
+          <t>235,47%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>261,67%</t>
+          <t>261,41%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 343,66</t>
+          <t>-3,36; 415,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>87,96; 650,8</t>
+          <t>91,33; 715,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-43,46; 146,66</t>
+          <t>-43,01; 161,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>99,88; 491,23</t>
+          <t>105,34; 521,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 162,86</t>
+          <t>0,19; 166,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>142,97; 472,72</t>
+          <t>141,06; 461,3</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>8,67</t>
+          <t>8,31</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6,16</t>
+          <t>6,28</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,2</t>
+          <t>7,13</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 2,17</t>
+          <t>-13,06; 1,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 16,8</t>
+          <t>-1,82; 16,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 2,19</t>
+          <t>-11,39; 2,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 12,01</t>
+          <t>-1,14; 12,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 0,46</t>
+          <t>-10,17; 0,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,61; 12,31</t>
+          <t>0,69; 11,92</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>106,21%</t>
+          <t>101,85%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>92,44%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-92,54; 206,85</t>
+          <t>-100,0; 110,18</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-21,83; 429,3</t>
+          <t>-18,36; 456,49</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-90,97; 119,06</t>
+          <t>-88,63; 96,89</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,13; 357,52</t>
+          <t>-12,25; 442,91</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-83,56; 19,57</t>
+          <t>-85,62; 24,76</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,12; 284,5</t>
+          <t>3,66; 248,52</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>19,76</t>
+          <t>19,16</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18,93</t>
+          <t>18,71</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,61</t>
+          <t>19,16</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 7,08</t>
+          <t>-8,01; 7,71</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>10,87; 28,63</t>
+          <t>9,58; 26,61</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 7,17</t>
+          <t>-4,53; 6,99</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12,42; 24,78</t>
+          <t>12,2; 24,98</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 5,05</t>
+          <t>-3,77; 5,49</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,92; 24,67</t>
+          <t>13,87; 24,08</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>207,32%</t>
+          <t>201,03%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>390,64%</t>
+          <t>386,21%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>281,31%</t>
+          <t>274,82%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-62,92; 140,02</t>
+          <t>-60,58; 155,16</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>58,13; 555,51</t>
+          <t>62,45; 539,09</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-63,38; 305,18</t>
+          <t>-59,02; 321,67</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>134,34; 1004,19</t>
+          <t>126,68; 1098,8</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-49,22; 107,69</t>
+          <t>-43,66; 112,37</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>129,96; 530,92</t>
+          <t>132,01; 516,31</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>29,41</t>
+          <t>29,48</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15,08</t>
+          <t>30,11</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,35</t>
+          <t>29,8</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,94; 14,33</t>
+          <t>2,44; 14,62</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>22,36; 36,06</t>
+          <t>22,74; 34,98</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 7,74</t>
+          <t>-2,55; 7,57</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 31,79</t>
+          <t>25,2; 35,94</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,12; 8,96</t>
+          <t>1,35; 9,04</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,61; 31,52</t>
+          <t>26,08; 33,92</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>389,82%</t>
+          <t>390,77%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>196,96%</t>
+          <t>393,3%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>267,53%</t>
+          <t>391,81%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>14,0; 311,62</t>
+          <t>18,65; 310,35</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>198,86; 802,32</t>
+          <t>181,48; 728,22</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-27,44; 141,88</t>
+          <t>-28,23; 148,06</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-27,04; 461,47</t>
+          <t>230,72; 776,64</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>8,29; 150,14</t>
+          <t>13,07; 155,54</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>59,79; 462,52</t>
+          <t>259,36; 620,79</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>56,84</t>
+          <t>30,56</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>32,53</t>
+          <t>32,89</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>48,44</t>
+          <t>31,95</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 2,83</t>
+          <t>-7,83; 2,81</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>29,24; 82,19</t>
+          <t>23,14; 36,35</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 1,81</t>
+          <t>-4,04; 2,03</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>27,54; 36,86</t>
+          <t>28,57; 37,71</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 1,58</t>
+          <t>-4,68; 1,21</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>30,36; 69,68</t>
+          <t>28,19; 35,89</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>529,81%</t>
+          <t>284,89%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>706,37%</t>
+          <t>714,21%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>661,38%</t>
+          <t>436,2%</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-54,22; 38,62</t>
+          <t>-57,99; 35,61</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>249,98; 1647,92</t>
+          <t>151,19; 511,57</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-66,38; 62,99</t>
+          <t>-64,58; 71,61</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>391,52; 1384,25</t>
+          <t>398,38; 1379,67</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-51,45; 29,57</t>
+          <t>-51,81; 21,93</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>369,59; 1251,06</t>
+          <t>285,16; 661,32</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>36,12</t>
+          <t>26,58</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>19,02</t>
+          <t>22,76</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>27,4</t>
+          <t>24,63</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 4,71</t>
+          <t>-0,38; 4,77</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>25,9; 55,91</t>
+          <t>23,7; 29,4</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,96</t>
+          <t>-2,1; 1,92</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>9,33; 22,98</t>
+          <t>20,62; 25,12</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 2,69</t>
+          <t>-0,63; 2,66</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>20,61; 40,95</t>
+          <t>22,86; 26,44</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>379,09%</t>
+          <t>278,95%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>253,56%</t>
+          <t>303,47%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>325,88%</t>
+          <t>292,94%</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 56,63</t>
+          <t>-4,16; 58,01</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>252,2; 661,52</t>
+          <t>207,12; 366,29</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 29,74</t>
+          <t>-25,54; 29,36</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>140,99; 342,01</t>
+          <t>231,93; 400,83</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 36,06</t>
+          <t>-6,98; 34,72</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>233,98; 505,67</t>
+          <t>239,76; 354,41</t>
         </is>
       </c>
     </row>
